--- a/data/gravel/Cannondale Topstone 2025.xlsx
+++ b/data/gravel/Cannondale Topstone 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0145FE92-C659-D349-9A6E-74A995D779EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{966E6268-B9C8-BE40-ABFA-0B84C86EFA1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2160" yWindow="900" windowWidth="26640" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="112">
   <si>
     <t>brand</t>
   </si>
@@ -366,6 +366,9 @@
   </si>
   <si>
     <t>a8:g36</t>
+  </si>
+  <si>
+    <t>https://embed.widencdn.net/img/dorelrl/pskntxaef9/1700px@1x/C25_C15235U_Topstone_2_2x_SGR_PD.webp?color=C1C2BD&amp;q=99</t>
   </si>
 </sst>
 </file>
@@ -766,6 +769,11 @@
         <v>98</v>
       </c>
     </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>111</v>
+      </c>
+    </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
@@ -993,7 +1001,7 @@
         <v>D Head Tube Angle</v>
       </c>
       <c r="C13">
-        <f t="shared" ref="C13:G15" si="9">K13</f>
+        <f t="shared" ref="C13:C15" si="9">K13</f>
         <v>70</v>
       </c>
       <c r="D13">
@@ -1137,23 +1145,23 @@
         <v>F Standover (cm)</v>
       </c>
       <c r="C16">
-        <f t="shared" ref="C15:C26" si="14">K16*10</f>
+        <f t="shared" ref="C16:C26" si="14">K16*10</f>
         <v>703</v>
       </c>
       <c r="D16">
-        <f t="shared" ref="D15:D26" si="15">L16*10</f>
+        <f t="shared" ref="D16:D26" si="15">L16*10</f>
         <v>744</v>
       </c>
       <c r="E16">
-        <f t="shared" ref="E15:E26" si="16">M16*10</f>
+        <f t="shared" ref="E16:E26" si="16">M16*10</f>
         <v>784</v>
       </c>
       <c r="F16">
-        <f t="shared" ref="F15:F26" si="17">N16*10</f>
+        <f t="shared" ref="F16:F26" si="17">N16*10</f>
         <v>824</v>
       </c>
       <c r="G16">
-        <f t="shared" ref="G15:G26" si="18">O16*10</f>
+        <f t="shared" ref="G16:G26" si="18">O16*10</f>
         <v>864</v>
       </c>
       <c r="J16" s="2" t="s">

--- a/data/gravel/Cannondale Topstone 2025.xlsx
+++ b/data/gravel/Cannondale Topstone 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{966E6268-B9C8-BE40-ABFA-0B84C86EFA1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA907FA5-D3F7-614C-ADD7-FA72FDC2B534}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2160" yWindow="900" windowWidth="26640" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="114">
   <si>
     <t>brand</t>
   </si>
@@ -369,6 +369,12 @@
   </si>
   <si>
     <t>https://embed.widencdn.net/img/dorelrl/pskntxaef9/1700px@1x/C25_C15235U_Topstone_2_2x_SGR_PD.webp?color=C1C2BD&amp;q=99</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Wilton, Connecticut, USA</t>
   </si>
 </sst>
 </file>
@@ -723,7 +729,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P76"/>
+  <dimension ref="A1:P77"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -2059,6 +2065,14 @@
         <v>96</v>
       </c>
     </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>112</v>
+      </c>
+      <c r="B77" t="s">
+        <v>113</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Cannondale Topstone 2025.xlsx
+++ b/data/gravel/Cannondale Topstone 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA907FA5-D3F7-614C-ADD7-FA72FDC2B534}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21D9D64A-4E62-DA4E-894B-299369832192}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2160" yWindow="900" windowWidth="26640" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="120">
   <si>
     <t>brand</t>
   </si>
@@ -375,6 +375,24 @@
   </si>
   <si>
     <t>Wilton, Connecticut, USA</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -729,7 +747,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P77"/>
+  <dimension ref="A1:P83"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1913,163 +1931,193 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>46</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>95</v>
+        <v>114</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>47</v>
+        <v>115</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>48</v>
-      </c>
-      <c r="B55">
-        <v>27.2</v>
+        <v>116</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>49</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>90</v>
+        <v>117</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>50</v>
+        <v>118</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>51</v>
+        <v>119</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>52</v>
+        <v>46</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>54</v>
+        <v>48</v>
+      </c>
+      <c r="B61">
+        <v>27.2</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>56</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>91</v>
+        <v>50</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>58</v>
-      </c>
-      <c r="B65" s="3"/>
+        <v>52</v>
+      </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>59</v>
-      </c>
-      <c r="B66">
-        <v>2</v>
+        <v>53</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>61</v>
-      </c>
-      <c r="B68">
-        <v>1</v>
+        <v>55</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>62</v>
-      </c>
-      <c r="B69">
-        <v>3</v>
+        <v>56</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>63</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>90</v>
+        <v>57</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>64</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="B71" s="3"/>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>65</v>
+        <v>59</v>
+      </c>
+      <c r="B72">
+        <v>2</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B74">
-        <v>1599</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>68</v>
+        <v>62</v>
+      </c>
+      <c r="B75">
+        <v>3</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>67</v>
+      </c>
+      <c r="B80">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>69</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
         <v>112</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B83" t="s">
         <v>113</v>
       </c>
     </row>
